--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488215_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488215_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.6318</v>
+        <v>6.9366</v>
       </c>
       <c r="E2" t="n">
-        <v>5.6673</v>
+        <v>6.7013</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0355</v>
+        <v>0.2353</v>
       </c>
       <c r="G2" t="n">
         <v>3.3018</v>
@@ -610,13 +610,13 @@
         <v>1.1117</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1829</v>
+        <v>2.4877</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4303</v>
+        <v>1.4643</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7526</v>
+        <v>1.0234</v>
       </c>
       <c r="V2" t="n">
         <v>1.8883</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.9148</v>
+        <v>4.0618</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3997</v>
+        <v>1.8668</v>
       </c>
       <c r="F3" t="n">
-        <v>2.515</v>
+        <v>2.195</v>
       </c>
       <c r="G3" t="n">
         <v>2.2484</v>
@@ -688,13 +688,13 @@
         <v>0.3706</v>
       </c>
       <c r="S3" t="n">
-        <v>2.9066</v>
+        <v>2.0537</v>
       </c>
       <c r="T3" t="n">
-        <v>1.7397</v>
+        <v>1.2069</v>
       </c>
       <c r="U3" t="n">
-        <v>1.1669</v>
+        <v>0.8468</v>
       </c>
       <c r="V3" t="n">
         <v>0.3155</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. MIAVIVULULU NZIKULU</t>
+          <t>M. MOLINA LOPEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9041</v>
+        <v>0.7216</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4871</v>
+        <v>-0.8347</v>
       </c>
       <c r="F5" t="n">
-        <v>0.417</v>
+        <v>1.5563</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0361</v>
+        <v>-0.4554</v>
       </c>
       <c r="H5" t="n">
-        <v>1.0898</v>
+        <v>-1.4293</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.1259</v>
+        <v>0.974</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3576</v>
+        <v>-1.094</v>
       </c>
       <c r="K5" t="n">
-        <v>1.8848</v>
+        <v>-1.1769</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5272</v>
+        <v>0.0829</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3937</v>
+        <v>0.6385999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.795</v>
+        <v>-0.2524</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5987</v>
+        <v>0.891</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.297</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.7793</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4823</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>3.2367</v>
+        <v>0.6211</v>
       </c>
       <c r="T5" t="n">
-        <v>2.2794</v>
+        <v>0.2593</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9572000000000001</v>
+        <v>0.3619</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0005</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6294</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6289</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. GEDEAO YIMBU</t>
+          <t>J. MIAVIVULULU NZIKULU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8229</v>
+        <v>0.636</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1344</v>
+        <v>0.3667</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3115</v>
+        <v>0.2693</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0361</v>
+        <v>-0.0361</v>
       </c>
       <c r="H6" t="n">
-        <v>2.1756</v>
+        <v>1.0898</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.1394</v>
+        <v>-1.1259</v>
       </c>
       <c r="J6" t="n">
-        <v>3.2827</v>
+        <v>1.3576</v>
       </c>
       <c r="K6" t="n">
-        <v>2.4947</v>
+        <v>1.8848</v>
       </c>
       <c r="L6" t="n">
-        <v>0.788</v>
+        <v>-0.5272</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.2465</v>
+        <v>-1.3937</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3191</v>
+        <v>-0.795</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.9274</v>
+        <v>-0.5987</v>
       </c>
       <c r="P6" t="n">
-        <v>-4.2616</v>
+        <v>-1.297</v>
       </c>
       <c r="Q6" t="n">
-        <v>-5.5586</v>
+        <v>-2.7793</v>
       </c>
       <c r="R6" t="n">
-        <v>1.297</v>
+        <v>1.4823</v>
       </c>
       <c r="S6" t="n">
-        <v>4.9933</v>
+        <v>1.9685</v>
       </c>
       <c r="T6" t="n">
-        <v>3.0964</v>
+        <v>1.159</v>
       </c>
       <c r="U6" t="n">
-        <v>1.8968</v>
+        <v>0.8095</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.945</v>
+        <v>0.0005</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3139</v>
+        <v>0.6294</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2589</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. MOLINA LOPEZ</t>
+          <t>A. GALLEGO CONTRERAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1614</v>
+        <v>-0.1068</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.4222</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2608</v>
+        <v>-0.0189</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4554</v>
+        <v>-0.0857</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.4293</v>
+        <v>-0.1932</v>
       </c>
       <c r="I7" t="n">
-        <v>0.974</v>
+        <v>0.1076</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.094</v>
+        <v>0.0215</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.1769</v>
+        <v>0.0215</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0829</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6385999999999999</v>
+        <v>-0.1071</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2524</v>
+        <v>-0.2147</v>
       </c>
       <c r="O7" t="n">
-        <v>0.891</v>
+        <v>0.1076</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5558999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5558999999999999</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2619</v>
+        <v>-0.0211</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3283</v>
+        <v>-0.1094</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0664</v>
+        <v>0.0883</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. GALLEGO CONTRERAS</t>
+          <t>J. PINILLA NUNEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2053</v>
+        <v>-0.1084</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.08799999999999999</v>
+        <v>-1.1067</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1173</v>
+        <v>0.9982</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0857</v>
+        <v>-3.3315</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1932</v>
+        <v>-1.4653</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1076</v>
+        <v>-1.8662</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0215</v>
+        <v>-2.4831</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0215</v>
+        <v>-0.6703</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-1.8128</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1071</v>
+        <v>-0.8484</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2147</v>
+        <v>-0.795</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1076</v>
+        <v>-0.0534</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-3.1499</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-4.6322</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.4823</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1196</v>
+        <v>1.0231</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1094</v>
+        <v>0.6588000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0102</v>
+        <v>0.3643</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>5.3498</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>5.3498</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. PINILLA NUNEZ</t>
+          <t>R. CARRETERO GONZALEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3646</v>
+        <v>-1.046</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0427</v>
+        <v>0.1778</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6782</v>
+        <v>-1.2238</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.3315</v>
+        <v>-1.6222</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.4653</v>
+        <v>-1.5639</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.8662</v>
+        <v>-0.0583</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.4831</v>
+        <v>-0.3583</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6703</v>
+        <v>-0.5455</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.8128</v>
+        <v>0.1872</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8484</v>
+        <v>-1.264</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.795</v>
+        <v>-1.0184</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0534</v>
+        <v>-0.2456</v>
       </c>
       <c r="P9" t="n">
-        <v>-3.1499</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.6322</v>
+        <v>-0.9264</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4823</v>
+        <v>0.3706</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.233</v>
+        <v>0.5021</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2773</v>
+        <v>0.2036</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0442</v>
+        <v>0.2984</v>
       </c>
       <c r="V9" t="n">
-        <v>5.3498</v>
+        <v>0.63</v>
       </c>
       <c r="W9" t="n">
-        <v>5.3498</v>
+        <v>1.2589</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. CARRETERO GONZALEZ</t>
+          <t>M. GEDEAO YIMBU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4394</v>
+        <v>-1.2376</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0799</v>
+        <v>-0.2366</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5193</v>
+        <v>-1.0009</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.6222</v>
+        <v>1.0361</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.5639</v>
+        <v>2.1756</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0583</v>
+        <v>-1.1394</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3583</v>
+        <v>3.2827</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5455</v>
+        <v>2.4947</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1872</v>
+        <v>0.788</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.264</v>
+        <v>-2.2465</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.0184</v>
+        <v>-0.3191</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2456</v>
+        <v>-1.9274</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-4.2616</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9264</v>
+        <v>-5.5586</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3706</v>
+        <v>1.297</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1087</v>
+        <v>2.9329</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1057</v>
+        <v>1.7254</v>
       </c>
       <c r="U10" t="n">
-        <v>0.003</v>
+        <v>1.2074</v>
       </c>
       <c r="V10" t="n">
-        <v>0.63</v>
+        <v>-0.945</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2589</v>
+        <v>0.3139</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6289</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.3859</v>
+        <v>-2.8668</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.0864</v>
+        <v>-3.4441</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7004</v>
+        <v>0.5773</v>
       </c>
       <c r="G11" t="n">
         <v>-2.8809</v>
@@ -1312,13 +1312,13 @@
         <v>1.6676</v>
       </c>
       <c r="S11" t="n">
-        <v>2.1451</v>
+        <v>2.6643</v>
       </c>
       <c r="T11" t="n">
-        <v>1.0284</v>
+        <v>1.6707</v>
       </c>
       <c r="U11" t="n">
-        <v>1.1167</v>
+        <v>0.9935</v>
       </c>
       <c r="V11" t="n">
         <v>0.3144</v>
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>9.2273</v>
+        <v>9.5007</v>
       </c>
       <c r="E12" t="n">
-        <v>5.639399999999999</v>
+        <v>5.912799999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>3.5878</v>
+        <v>3.587800000000001</v>
       </c>
       <c r="G12" t="n">
         <v>0.6847999999999996</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.2757999999999999</v>
+        <v>-0.2757999999999997</v>
       </c>
       <c r="I12" t="n">
         <v>0.9608999999999996</v>
@@ -1369,7 +1369,7 @@
         <v>5.382000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>3.531299999999999</v>
+        <v>3.531300000000001</v>
       </c>
       <c r="M12" t="n">
         <v>-8.228300000000001</v>
@@ -1390,16 +1390,16 @@
         <v>8.337999999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>13.9588</v>
+        <v>14.2323</v>
       </c>
       <c r="T12" t="n">
-        <v>7.9649</v>
+        <v>8.2386</v>
       </c>
       <c r="U12" t="n">
-        <v>5.993600000000001</v>
+        <v>5.9935</v>
       </c>
       <c r="V12" t="n">
-        <v>7.5535</v>
+        <v>7.553500000000001</v>
       </c>
       <c r="W12" t="n">
         <v>10.0691</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.1321</v>
+        <v>2.0599</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5026</v>
+        <v>1.2088</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6294999999999999</v>
+        <v>0.8511</v>
       </c>
       <c r="G14" t="n">
         <v>1.3016</v>
@@ -1546,13 +1546,13 @@
         <v>3.891</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.1341</v>
+        <v>-2.2063</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5334</v>
+        <v>-0.8272</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.6007</v>
+        <v>-1.3791</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>O. KANTE</t>
+          <t>F. BENÍTEZ SIERRA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9671</v>
+        <v>0.3221</v>
       </c>
       <c r="E15" t="n">
-        <v>1.1891</v>
+        <v>0.3221</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2219</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.5901999999999999</v>
+        <v>0.3221</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.326</v>
+        <v>0.3221</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7358</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1.6481</v>
+        <v>0.3221</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.0997</v>
+        <v>0.3221</v>
       </c>
       <c r="L15" t="n">
-        <v>2.7478</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.2382</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2263</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.012</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.0382</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.9646</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4636</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.153</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3106</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.9444</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>F. BENÍTEZ SIERRA</t>
+          <t>M. BRAVO ORTEGA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3221</v>
+        <v>0.0323</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3221</v>
+        <v>-0.9225</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>0.9548</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3221</v>
+        <v>1.3341</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3221</v>
+        <v>-0.1375</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1.4716</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3221</v>
+        <v>0.8784999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3221</v>
+        <v>0.7126</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>0.1659</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>0.4556</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>-0.8501</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.3057</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.297</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-0.7464</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>0.0519</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>-0.7984</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. BRAVO ORTEGA</t>
+          <t>I. PEREZ SAENZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1784</v>
+        <v>-0.3932</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.6287</v>
+        <v>0.0215</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8071</v>
+        <v>-0.4147</v>
       </c>
       <c r="G17" t="n">
-        <v>1.3341</v>
+        <v>-0.3932</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1375</v>
+        <v>0.0215</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4716</v>
+        <v>-0.4147</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8784999999999999</v>
+        <v>0.0215</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7126</v>
+        <v>0.0215</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1659</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4556</v>
+        <v>-0.4147</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8501</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>1.3057</v>
+        <v>-0.4147</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.5558999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.297</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6004</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3457</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.9461000000000001</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0.0005</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.0005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. PEREZ SAENZ</t>
+          <t>C. CORRALES GARCIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3932</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0215</v>
+        <v>-0.2736</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4147</v>
+        <v>-0.4164</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3932</v>
+        <v>-0.1219</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0215</v>
+        <v>-0.1219</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4147</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0215</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0215</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4147</v>
+        <v>-0.1219</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-0.1219</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4147</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.3706</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>0.3706</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-0.6243</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>-0.2736</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>-0.3507</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. CORRALES GARCIA</t>
+          <t>O. KANTE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7146</v>
+        <v>-0.7754</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2736</v>
+        <v>0.2098</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.441</v>
+        <v>-0.9852</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1219</v>
+        <v>-0.5901999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1219</v>
+        <v>-1.326</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>0.7358</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1.6481</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>-1.0997</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.7478</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1219</v>
+        <v>-2.2382</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1219</v>
+        <v>-0.2263</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>-2.012</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3706</v>
+        <v>2.0382</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3706</v>
+        <v>2.9646</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6489</v>
+        <v>-1.279</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2736</v>
+        <v>-0.8263</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3753</v>
+        <v>-0.4527</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3144</v>
+        <v>-0.9444</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.3144</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2799</v>
+        <v>-1.1333</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.598</v>
+        <v>-0.4021</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6819</v>
+        <v>-0.7312</v>
       </c>
       <c r="G20" t="n">
         <v>-0.1672</v>
@@ -2014,13 +2014,13 @@
         <v>1.4823</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.3721</v>
+        <v>-1.2255</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9849</v>
+        <v>-0.789</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3873</v>
+        <v>-0.4365</v>
       </c>
       <c r="V20" t="n">
         <v>0.63</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6083</v>
+        <v>-2.0442</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.7264</v>
+        <v>-2.3346</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1181</v>
+        <v>0.2904</v>
       </c>
       <c r="G21" t="n">
         <v>-1.7553</v>
@@ -2092,13 +2092,13 @@
         <v>2.7793</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.3734</v>
+        <v>-1.8093</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.3679</v>
+        <v>-0.9762</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.0055</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2589</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.0116</v>
+        <v>-2.227</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.0887</v>
+        <v>-1.5011</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9229000000000001</v>
+        <v>-0.726</v>
       </c>
       <c r="G22" t="n">
         <v>-1.7281</v>
@@ -2170,13 +2170,13 @@
         <v>2.9646</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.9887</v>
+        <v>-2.2042</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.3467</v>
+        <v>-0.7592</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.642</v>
+        <v>-1.445</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2594</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.6711</v>
+        <v>-3.3762</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.8378</v>
+        <v>-2.7398</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8333</v>
+        <v>-0.6364</v>
       </c>
       <c r="G23" t="n">
         <v>-2.1462</v>
@@ -2248,13 +2248,13 @@
         <v>3.3352</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.0623</v>
+        <v>-1.7674</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9674</v>
+        <v>-0.8695000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.0948</v>
+        <v>-0.8979</v>
       </c>
       <c r="V23" t="n">
         <v>-0.945</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.5806</v>
+        <v>-4.4346</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.9024</v>
+        <v>-0.6086</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.6783</v>
+        <v>-3.826</v>
       </c>
       <c r="G24" t="n">
         <v>-0.1732</v>
@@ -2326,13 +2326,13 @@
         <v>2.2234</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.2424</v>
+        <v>-2.0963</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.0184</v>
+        <v>-0.7247</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.2239</v>
+        <v>-1.3716</v>
       </c>
       <c r="V24" t="n">
         <v>-3.4621</v>
@@ -2362,22 +2362,22 @@
         <v>-9.2272</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.5879</v>
+        <v>-3.587700000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.6393</v>
+        <v>-5.6396</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.6850999999999989</v>
+        <v>-0.6850999999999998</v>
       </c>
       <c r="H25" t="n">
         <v>0.2758999999999997</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.9609000000000004</v>
+        <v>-0.9609</v>
       </c>
       <c r="J25" t="n">
-        <v>8.228300000000001</v>
+        <v>8.228299999999999</v>
       </c>
       <c r="K25" t="n">
         <v>5.657800000000001</v>
@@ -2386,13 +2386,13 @@
         <v>2.5704</v>
       </c>
       <c r="M25" t="n">
-        <v>-8.9132</v>
+        <v>-8.913199999999998</v>
       </c>
       <c r="N25" t="n">
         <v>-5.3819</v>
       </c>
       <c r="O25" t="n">
-        <v>-3.531400000000001</v>
+        <v>-3.5314</v>
       </c>
       <c r="P25" t="n">
         <v>12.9701</v>
@@ -2407,10 +2407,10 @@
         <v>-13.9587</v>
       </c>
       <c r="T25" t="n">
-        <v>-5.993599999999999</v>
+        <v>-5.993800000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>-7.965</v>
+        <v>-7.965100000000001</v>
       </c>
       <c r="V25" t="n">
         <v>-7.553700000000001</v>
